--- a/kemsyn_google_form.xlsx
+++ b/kemsyn_google_form.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\BAKALIST\kemsyn\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{104A4BA4-A4A1-4355-8A5C-3A83189256EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41B3178C-1750-4EBF-A6D2-241A39A9C8DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{D5BA862F-09D3-4224-9627-19A740074978}"/>
   </bookViews>
@@ -4071,10 +4071,10 @@
         <v>173.44</v>
       </c>
       <c r="F121" s="2">
-        <v>14.87</v>
+        <v>17.75</v>
       </c>
       <c r="H121" s="2">
-        <v>14.87</v>
+        <v>17.75</v>
       </c>
     </row>
     <row r="122" spans="1:8" x14ac:dyDescent="0.25">
@@ -5543,10 +5543,10 @@
         <v>9.66</v>
       </c>
       <c r="F185" s="2">
-        <v>4.6399999999999997</v>
+        <v>5.0199999999999996</v>
       </c>
       <c r="H185" s="2">
-        <v>4.6399999999999997</v>
+        <v>5.0199999999999996</v>
       </c>
     </row>
     <row r="186" spans="1:8" x14ac:dyDescent="0.25">
@@ -5566,10 +5566,10 @@
         <v>31.88</v>
       </c>
       <c r="F186" s="2">
-        <v>8.3699999999999992</v>
+        <v>9.1999999999999993</v>
       </c>
       <c r="H186" s="2">
-        <v>8.3699999999999992</v>
+        <v>9.1999999999999993</v>
       </c>
     </row>
     <row r="187" spans="1:8" x14ac:dyDescent="0.25">
@@ -5750,10 +5750,10 @@
         <v>839.96</v>
       </c>
       <c r="F194" s="2">
-        <v>96.88</v>
+        <v>104.33</v>
       </c>
       <c r="H194" s="2">
-        <v>96.88</v>
+        <v>104.33</v>
       </c>
     </row>
     <row r="195" spans="1:8" x14ac:dyDescent="0.25">
